--- a/public/plantillas/Makro/offer_template PT.xlsx
+++ b/public/plantillas/Makro/offer_template PT.xlsx
@@ -1832,25 +1832,404 @@
       </c>
     </row>
     <row r="30">
-      <c r="G30" s="4"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641312</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F30" s="0">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4">
+        <v>105.69</v>
+      </c>
+      <c r="H30" s="0">
+        <v>2</v>
+      </c>
+      <c r="I30" s="0">
+        <v>3</v>
+      </c>
+      <c r="L30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N30" s="0">
+        <v>103</v>
+      </c>
+      <c r="O30" s="0">
+        <v>101</v>
+      </c>
+      <c r="P30" s="0">
+        <v>99</v>
+      </c>
+      <c r="Q30" s="0">
+        <v>97</v>
+      </c>
+      <c r="V30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GENVIO</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="G31" s="4"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641336</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F31" s="0">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4">
+        <v>105.69</v>
+      </c>
+      <c r="H31" s="0">
+        <v>2</v>
+      </c>
+      <c r="I31" s="0">
+        <v>3</v>
+      </c>
+      <c r="L31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N31" s="0">
+        <v>103</v>
+      </c>
+      <c r="O31" s="0">
+        <v>101</v>
+      </c>
+      <c r="P31" s="0">
+        <v>99</v>
+      </c>
+      <c r="Q31" s="0">
+        <v>97</v>
+      </c>
+      <c r="V31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GENVIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641329</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F32" s="0">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5">
+        <v>105.69</v>
+      </c>
+      <c r="H32" s="0">
+        <v>2</v>
+      </c>
+      <c r="I32" s="0">
+        <v>3</v>
+      </c>
+      <c r="L32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N32" s="0">
+        <v>103</v>
+      </c>
+      <c r="O32" s="0">
+        <v>101</v>
+      </c>
+      <c r="P32" s="0">
+        <v>99</v>
+      </c>
+      <c r="Q32" s="0">
+        <v>97</v>
+      </c>
+      <c r="V32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GENVIO</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15.5">
-      <c r="G33" s="3"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641343</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F33" s="0">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>105.69</v>
+      </c>
+      <c r="H33" s="0">
+        <v>2</v>
+      </c>
+      <c r="I33" s="0">
+        <v>3</v>
+      </c>
+      <c r="L33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N33" s="0">
+        <v>103</v>
+      </c>
+      <c r="O33" s="0">
+        <v>101</v>
+      </c>
+      <c r="P33" s="0">
+        <v>99</v>
+      </c>
+      <c r="Q33" s="0">
+        <v>97</v>
+      </c>
+      <c r="V33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GENVIO</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15.5">
-      <c r="G34" s="3"/>
+      <c r="A34" s="2">
+        <v>8437027641350</v>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F34" s="0">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3">
+        <v>141.46</v>
+      </c>
+      <c r="H34" s="0">
+        <v>2</v>
+      </c>
+      <c r="I34" s="0">
+        <v>3</v>
+      </c>
+      <c r="L34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N34" s="0">
+        <v>139</v>
+      </c>
+      <c r="O34" s="0">
+        <v>137</v>
+      </c>
+      <c r="P34" s="0">
+        <v>135</v>
+      </c>
+      <c r="Q34" s="0">
+        <v>133</v>
+      </c>
+      <c r="V34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GENVIO</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15.5">
-      <c r="G35" s="3"/>
+      <c r="A35" s="2">
+        <v>8437027641374</v>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F35" s="0">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>141.46</v>
+      </c>
+      <c r="H35" s="0">
+        <v>2</v>
+      </c>
+      <c r="I35" s="0">
+        <v>3</v>
+      </c>
+      <c r="L35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N35" s="0">
+        <v>139</v>
+      </c>
+      <c r="O35" s="0">
+        <v>137</v>
+      </c>
+      <c r="P35" s="0">
+        <v>135</v>
+      </c>
+      <c r="Q35" s="0">
+        <v>133</v>
+      </c>
+      <c r="V35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GENVIO</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15.5">
-      <c r="G36" s="3"/>
+      <c r="A36" s="2">
+        <v>8437027641367</v>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F36" s="0">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3">
+        <v>141.46</v>
+      </c>
+      <c r="H36" s="0">
+        <v>2</v>
+      </c>
+      <c r="I36" s="0">
+        <v>3</v>
+      </c>
+      <c r="L36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N36" s="0">
+        <v>139</v>
+      </c>
+      <c r="O36" s="0">
+        <v>137</v>
+      </c>
+      <c r="P36" s="0">
+        <v>135</v>
+      </c>
+      <c r="Q36" s="0">
+        <v>133</v>
+      </c>
+      <c r="V36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GENVIO</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15.5">
-      <c r="G37" s="3"/>
+      <c r="A37" s="2">
+        <v>8437027641381</v>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F37" s="0">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3">
+        <v>141.46</v>
+      </c>
+      <c r="H37" s="0">
+        <v>2</v>
+      </c>
+      <c r="I37" s="0">
+        <v>3</v>
+      </c>
+      <c r="L37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N37" s="0">
+        <v>139</v>
+      </c>
+      <c r="O37" s="0">
+        <v>137</v>
+      </c>
+      <c r="P37" s="0">
+        <v>135</v>
+      </c>
+      <c r="Q37" s="0">
+        <v>133</v>
+      </c>
+      <c r="V37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GENVIO</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15.5">
       <c r="G38" s="3"/>

--- a/public/plantillas/Makro/offer_template PT.xlsx
+++ b/public/plantillas/Makro/offer_template PT.xlsx
@@ -2232,34 +2232,514 @@
       </c>
     </row>
     <row r="38" ht="15.5">
-      <c r="G38" s="3"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641534</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F38" s="0">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3">
+        <v>97.56</v>
+      </c>
+      <c r="H38" s="0">
+        <v>2</v>
+      </c>
+      <c r="I38" s="0">
+        <v>3</v>
+      </c>
+      <c r="L38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N38" s="0">
+        <v>94.63</v>
+      </c>
+      <c r="O38" s="0">
+        <v>93.66</v>
+      </c>
+      <c r="P38" s="0">
+        <v>92.68</v>
+      </c>
+      <c r="Q38" s="0">
+        <v>91.71</v>
+      </c>
+      <c r="V38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15.5">
-      <c r="G39" s="3"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641480</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F39" s="0">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3">
+        <v>96.75</v>
+      </c>
+      <c r="H39" s="0">
+        <v>2</v>
+      </c>
+      <c r="I39" s="0">
+        <v>3</v>
+      </c>
+      <c r="L39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N39" s="0">
+        <v>93.85</v>
+      </c>
+      <c r="O39" s="0">
+        <v>92.88</v>
+      </c>
+      <c r="P39" s="0">
+        <v>91.91</v>
+      </c>
+      <c r="Q39" s="0">
+        <v>90.95</v>
+      </c>
+      <c r="V39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMALL</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15.5">
-      <c r="G40" s="3"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641497</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F40" s="0">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3">
+        <v>243.9</v>
+      </c>
+      <c r="H40" s="0">
+        <v>2</v>
+      </c>
+      <c r="I40" s="0">
+        <v>3</v>
+      </c>
+      <c r="L40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N40" s="0">
+        <v>236.58</v>
+      </c>
+      <c r="O40" s="0">
+        <v>234.14</v>
+      </c>
+      <c r="P40" s="0">
+        <v>231.71</v>
+      </c>
+      <c r="Q40" s="0">
+        <v>229.27</v>
+      </c>
+      <c r="V40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15.5">
-      <c r="G41" s="3"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641442</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F41" s="0">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
+        <v>243.9</v>
+      </c>
+      <c r="H41" s="0">
+        <v>2</v>
+      </c>
+      <c r="I41" s="0">
+        <v>3</v>
+      </c>
+      <c r="L41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N41" s="0">
+        <v>236.58</v>
+      </c>
+      <c r="O41" s="0">
+        <v>234.14</v>
+      </c>
+      <c r="P41" s="0">
+        <v>231.71</v>
+      </c>
+      <c r="Q41" s="0">
+        <v>229.27</v>
+      </c>
+      <c r="V41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15.5">
-      <c r="G42" s="3"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641503</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F42" s="0">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>145.53</v>
+      </c>
+      <c r="H42" s="0">
+        <v>2</v>
+      </c>
+      <c r="I42" s="0">
+        <v>3</v>
+      </c>
+      <c r="L42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N42" s="0">
+        <v>141.16</v>
+      </c>
+      <c r="O42" s="0">
+        <v>139.71</v>
+      </c>
+      <c r="P42" s="0">
+        <v>138.25</v>
+      </c>
+      <c r="Q42" s="0">
+        <v>136.8</v>
+      </c>
+      <c r="V42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15.5">
-      <c r="G43" s="3"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641459</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F43" s="0">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <v>145.53</v>
+      </c>
+      <c r="H43" s="0">
+        <v>2</v>
+      </c>
+      <c r="I43" s="0">
+        <v>3</v>
+      </c>
+      <c r="L43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N43" s="0">
+        <v>141.16</v>
+      </c>
+      <c r="O43" s="0">
+        <v>139.71</v>
+      </c>
+      <c r="P43" s="0">
+        <v>138.25</v>
+      </c>
+      <c r="Q43" s="0">
+        <v>136.8</v>
+      </c>
+      <c r="V43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15.5">
-      <c r="G44" s="3"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641510</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F44" s="0">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>161.79</v>
+      </c>
+      <c r="H44" s="0">
+        <v>2</v>
+      </c>
+      <c r="I44" s="0">
+        <v>3</v>
+      </c>
+      <c r="L44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N44" s="0">
+        <v>156.94</v>
+      </c>
+      <c r="O44" s="0">
+        <v>155.32</v>
+      </c>
+      <c r="P44" s="0">
+        <v>153.7</v>
+      </c>
+      <c r="Q44" s="0">
+        <v>152.08</v>
+      </c>
+      <c r="V44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15.5">
-      <c r="G45" s="3"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641466</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F45" s="0">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
+        <v>162.6</v>
+      </c>
+      <c r="H45" s="0">
+        <v>2</v>
+      </c>
+      <c r="I45" s="0">
+        <v>3</v>
+      </c>
+      <c r="L45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N45" s="0">
+        <v>157.72</v>
+      </c>
+      <c r="O45" s="0">
+        <v>156.1</v>
+      </c>
+      <c r="P45" s="0">
+        <v>154.47</v>
+      </c>
+      <c r="Q45" s="0">
+        <v>152.84</v>
+      </c>
+      <c r="V45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15.5">
-      <c r="G46" s="3"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641527</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F46" s="0">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3">
+        <v>226.83</v>
+      </c>
+      <c r="H46" s="0">
+        <v>2</v>
+      </c>
+      <c r="I46" s="0">
+        <v>3</v>
+      </c>
+      <c r="L46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N46" s="0">
+        <v>220.03</v>
+      </c>
+      <c r="O46" s="0">
+        <v>217.76</v>
+      </c>
+      <c r="P46" s="0">
+        <v>215.49</v>
+      </c>
+      <c r="Q46" s="0">
+        <v>213.22</v>
+      </c>
+      <c r="V46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15.5">
-      <c r="G47" s="3"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8437027641473</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TwinThink</t>
+        </is>
+      </c>
+      <c r="F47" s="0">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>226.83</v>
+      </c>
+      <c r="H47" s="0">
+        <v>2</v>
+      </c>
+      <c r="I47" s="0">
+        <v>3</v>
+      </c>
+      <c r="L47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PT_MAIN</t>
+        </is>
+      </c>
+      <c r="M47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ES_MAIN</t>
+        </is>
+      </c>
+      <c r="N47" s="0">
+        <v>220.03</v>
+      </c>
+      <c r="O47" s="0">
+        <v>217.76</v>
+      </c>
+      <c r="P47" s="0">
+        <v>215.49</v>
+      </c>
+      <c r="Q47" s="0">
+        <v>213.22</v>
+      </c>
+      <c r="V47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGE</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15.5">
       <c r="G48" s="3"/>
